--- a/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.3_Log_Protection_Retention_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.3_Log_Protection_Retention_20260208.xlsx
@@ -18862,7 +18862,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PCI DSS: 12 months minimum</t>
+          <t>PCI DSS v4.0.1: 12 months minimum</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PCI DSS</t>
+          <t>PCI DSS v4.0.1</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       <formula1>"Security,Authentication,Admin,Application,System,Network,Database"</formula1>
     </dataValidation>
     <dataValidation sqref="C9:C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PCI DSS,HIPAA,SOX,GDPR,FADP,ISO 27001,None"</formula1>
+      <formula1>"PCI DSS v4.0.1,HIPAA,SOX,GDPR,FADP,ISO 27001,None"</formula1>
     </dataValidation>
     <dataValidation sqref="L9:L100 N9:N100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
